--- a/6_EDI/CrownGeometryHarvardForest_v2013.xlsx
+++ b/6_EDI/CrownGeometryHarvardForest_v2013.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitRepo\FlorestaR\dados\6_EDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D4E56F5-0A2C-45E6-BC52-EAECE7302522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7020CA-7754-451B-97F7-956505C6AC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BCB89E3D-8D38-4E78-9B30-F168ADFC3B11}"/>
   </bookViews>
@@ -211,34 +211,34 @@
     <t>PLT0037</t>
   </si>
   <si>
-    <t>si,offset,e</t>
+    <t>si_offset_e</t>
   </si>
   <si>
-    <t>si,offset,n</t>
+    <t>si_offset_n</t>
   </si>
   <si>
-    <t>tree,easting</t>
+    <t>tree_easting</t>
   </si>
   <si>
-    <t>tree,northing</t>
+    <t>tree_northing</t>
   </si>
   <si>
-    <t>sensor,est,e</t>
+    <t>sensor_est_e</t>
   </si>
   <si>
-    <t>sensor,est,n</t>
+    <t>sensor_est_n</t>
   </si>
   <si>
-    <t>rad,in</t>
+    <t>rad_in</t>
   </si>
   <si>
-    <t>rad,out</t>
+    <t>rad_out</t>
   </si>
   <si>
-    <t>east,center</t>
+    <t>east_center</t>
   </si>
   <si>
-    <t>north,center</t>
+    <t>north_center</t>
   </si>
 </sst>
 </file>
@@ -1105,6 +1105,18 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">

--- a/6_EDI/CrownGeometryHarvardForest_v2013.xlsx
+++ b/6_EDI/CrownGeometryHarvardForest_v2013.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitRepo\FlorestaR\dados\6_EDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7020CA-7754-451B-97F7-956505C6AC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCEBCE4-2307-4A49-8A17-B968E4E85348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{BCB89E3D-8D38-4E78-9B30-F168ADFC3B11}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="72">
   <si>
     <t>date</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>PLT0050</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
   <si>
     <t>PLT0041</t>
@@ -1130,22 +1127,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" t="s">
-        <v>68</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -1157,10 +1154,10 @@
         <v>5</v>
       </c>
       <c r="M1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" t="s">
         <v>69</v>
-      </c>
-      <c r="N1" t="s">
-        <v>70</v>
       </c>
       <c r="O1" t="s">
         <v>6</v>
@@ -1169,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="Q1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" t="s">
         <v>71</v>
-      </c>
-      <c r="R1" t="s">
-        <v>72</v>
       </c>
       <c r="S1" t="s">
         <v>8</v>
@@ -1896,12 +1893,6 @@
       <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
       <c r="F14">
         <v>731592.9</v>
       </c>
@@ -2068,7 +2059,7 @@
         <v>41537</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -2127,7 +2118,7 @@
         <v>41537</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -2186,7 +2177,7 @@
         <v>41537</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -2245,7 +2236,7 @@
         <v>41537</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -2304,7 +2295,7 @@
         <v>41537</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -2363,7 +2354,7 @@
         <v>41537</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -2422,7 +2413,7 @@
         <v>41537</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -2481,10 +2472,10 @@
         <v>41537</v>
       </c>
       <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
         <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
       </c>
       <c r="D24">
         <v>599.00799559999996</v>
@@ -2540,10 +2531,10 @@
         <v>41537</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25">
         <v>605.99200440000004</v>
@@ -2599,17 +2590,11 @@
         <v>41537</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>14</v>
-      </c>
       <c r="F26">
         <v>731592.9</v>
       </c>
@@ -2648,9 +2633,6 @@
       </c>
       <c r="R26">
         <v>7.8174873000000006E-2</v>
-      </c>
-      <c r="S26" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
@@ -2658,7 +2640,7 @@
         <v>41537</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2717,7 +2699,7 @@
         <v>41537</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2776,10 +2758,10 @@
         <v>41537</v>
       </c>
       <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
         <v>19</v>
-      </c>
-      <c r="C29" t="s">
-        <v>20</v>
       </c>
       <c r="D29">
         <v>562.78802489999998</v>
@@ -2808,23 +2790,8 @@
       <c r="L29">
         <v>1.3</v>
       </c>
-      <c r="M29" t="s">
-        <v>14</v>
-      </c>
-      <c r="N29" t="s">
-        <v>14</v>
-      </c>
-      <c r="O29" t="s">
-        <v>14</v>
-      </c>
       <c r="P29">
         <v>168</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>14</v>
-      </c>
-      <c r="R29" t="s">
-        <v>14</v>
       </c>
       <c r="S29">
         <v>290978</v>
@@ -2835,10 +2802,10 @@
         <v>41537</v>
       </c>
       <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
         <v>19</v>
-      </c>
-      <c r="C30" t="s">
-        <v>20</v>
       </c>
       <c r="D30">
         <v>559.90502930000002</v>
@@ -2894,10 +2861,10 @@
         <v>41537</v>
       </c>
       <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
         <v>19</v>
-      </c>
-      <c r="C31" t="s">
-        <v>20</v>
       </c>
       <c r="D31">
         <v>557.34301760000005</v>
@@ -2953,10 +2920,10 @@
         <v>41537</v>
       </c>
       <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
         <v>19</v>
-      </c>
-      <c r="C32" t="s">
-        <v>20</v>
       </c>
       <c r="D32">
         <v>559.06896970000003</v>
@@ -3012,10 +2979,10 @@
         <v>41537</v>
       </c>
       <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
         <v>19</v>
-      </c>
-      <c r="C33" t="s">
-        <v>20</v>
       </c>
       <c r="D33">
         <v>558.05297849999999</v>
@@ -3071,10 +3038,10 @@
         <v>41537</v>
       </c>
       <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
         <v>19</v>
-      </c>
-      <c r="C34" t="s">
-        <v>20</v>
       </c>
       <c r="D34">
         <v>561.625</v>
@@ -3130,16 +3097,10 @@
         <v>41537</v>
       </c>
       <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
         <v>19</v>
-      </c>
-      <c r="C35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
       </c>
       <c r="F35">
         <v>731592.9</v>
@@ -3189,16 +3150,10 @@
         <v>41537</v>
       </c>
       <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
         <v>19</v>
-      </c>
-      <c r="C36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
       </c>
       <c r="F36">
         <v>731592.9</v>
@@ -3248,10 +3203,10 @@
         <v>41537</v>
       </c>
       <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
         <v>19</v>
-      </c>
-      <c r="C37" t="s">
-        <v>20</v>
       </c>
       <c r="D37">
         <v>565.94000240000003</v>
@@ -3307,10 +3262,10 @@
         <v>41537</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D38">
         <v>510.88500979999998</v>
@@ -3366,10 +3321,10 @@
         <v>41537</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D39">
         <v>509.45700069999998</v>
@@ -3397,12 +3352,6 @@
       </c>
       <c r="L39">
         <v>1.3</v>
-      </c>
-      <c r="M39" t="s">
-        <v>14</v>
-      </c>
-      <c r="N39" t="s">
-        <v>14</v>
       </c>
       <c r="O39">
         <v>3.67</v>
@@ -3425,10 +3374,10 @@
         <v>41537</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D40">
         <v>506.59600829999999</v>
@@ -3484,10 +3433,10 @@
         <v>41537</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D41">
         <v>511.45599370000002</v>
@@ -3543,7 +3492,7 @@
         <v>41537</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -3602,7 +3551,7 @@
         <v>41537</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -3661,7 +3610,7 @@
         <v>41537</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -3720,10 +3669,10 @@
         <v>41537</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D45">
         <v>516.12402340000006</v>
@@ -3779,10 +3728,10 @@
         <v>41537</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D46">
         <v>513.99902340000006</v>
@@ -3838,10 +3787,10 @@
         <v>41537</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47">
         <v>511.12899779999998</v>
@@ -3897,7 +3846,7 @@
         <v>41537</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
@@ -3956,7 +3905,7 @@
         <v>41537</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
@@ -4015,7 +3964,7 @@
         <v>41537</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -4074,7 +4023,7 @@
         <v>41537</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -4133,10 +4082,10 @@
         <v>41537</v>
       </c>
       <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" t="s">
         <v>22</v>
-      </c>
-      <c r="C52" t="s">
-        <v>23</v>
       </c>
       <c r="D52">
         <v>390.83099370000002</v>
@@ -4165,23 +4114,8 @@
       <c r="L52">
         <v>1.3</v>
       </c>
-      <c r="M52" t="s">
-        <v>14</v>
-      </c>
-      <c r="N52" t="s">
-        <v>14</v>
-      </c>
-      <c r="O52" t="s">
-        <v>14</v>
-      </c>
       <c r="P52">
         <v>166</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>14</v>
-      </c>
-      <c r="R52" t="s">
-        <v>14</v>
       </c>
       <c r="S52">
         <v>200501</v>
@@ -4192,7 +4126,7 @@
         <v>41537</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -4251,7 +4185,7 @@
         <v>41537</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -4310,10 +4244,10 @@
         <v>41537</v>
       </c>
       <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" t="s">
         <v>22</v>
-      </c>
-      <c r="C55" t="s">
-        <v>23</v>
       </c>
       <c r="D55">
         <v>386.86401369999999</v>
@@ -4369,10 +4303,10 @@
         <v>41537</v>
       </c>
       <c r="B56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" t="s">
         <v>22</v>
-      </c>
-      <c r="C56" t="s">
-        <v>23</v>
       </c>
       <c r="D56">
         <v>388.21301269999998</v>
@@ -4400,12 +4334,6 @@
       </c>
       <c r="L56">
         <v>1.3</v>
-      </c>
-      <c r="M56" t="s">
-        <v>14</v>
-      </c>
-      <c r="N56" t="s">
-        <v>14</v>
       </c>
       <c r="O56">
         <v>2.7</v>
@@ -4428,7 +4356,7 @@
         <v>41537</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -4487,10 +4415,10 @@
         <v>41537</v>
       </c>
       <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" t="s">
         <v>22</v>
-      </c>
-      <c r="C58" t="s">
-        <v>23</v>
       </c>
       <c r="D58">
         <v>390.81500240000003</v>
@@ -4546,7 +4474,7 @@
         <v>41537</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
@@ -4605,10 +4533,10 @@
         <v>41537</v>
       </c>
       <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" t="s">
         <v>24</v>
-      </c>
-      <c r="C60" t="s">
-        <v>25</v>
       </c>
       <c r="D60">
         <v>414.92800899999997</v>
@@ -4664,7 +4592,7 @@
         <v>41537</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -4723,7 +4651,7 @@
         <v>41537</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -4782,7 +4710,7 @@
         <v>41537</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -4841,10 +4769,10 @@
         <v>41537</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D64">
         <v>411.13000490000002</v>
@@ -4900,7 +4828,7 @@
         <v>41537</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -4959,10 +4887,10 @@
         <v>41537</v>
       </c>
       <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
         <v>27</v>
-      </c>
-      <c r="C66" t="s">
-        <v>28</v>
       </c>
       <c r="D66">
         <v>400.21798710000002</v>
@@ -5018,7 +4946,7 @@
         <v>41537</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5077,10 +5005,10 @@
         <v>41537</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D68">
         <v>407.4500122</v>
@@ -5136,10 +5064,10 @@
         <v>41537</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>404.37100220000002</v>
@@ -5195,10 +5123,10 @@
         <v>41537</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D70">
         <v>400.78601070000002</v>
@@ -5254,10 +5182,10 @@
         <v>41537</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71">
         <v>398.118988</v>
@@ -5313,7 +5241,7 @@
         <v>41537</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -5372,7 +5300,7 @@
         <v>41537</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -5431,7 +5359,7 @@
         <v>41537</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
@@ -5490,10 +5418,10 @@
         <v>41537</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75">
         <v>397.85900880000003</v>
@@ -5522,23 +5450,8 @@
       <c r="L75">
         <v>1.3</v>
       </c>
-      <c r="M75" t="s">
-        <v>14</v>
-      </c>
-      <c r="N75" t="s">
-        <v>14</v>
-      </c>
-      <c r="O75" t="s">
-        <v>14</v>
-      </c>
       <c r="P75">
         <v>320</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>14</v>
-      </c>
-      <c r="R75" t="s">
-        <v>14</v>
       </c>
       <c r="S75">
         <v>200368</v>
@@ -5549,7 +5462,7 @@
         <v>41537</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
@@ -5608,7 +5521,7 @@
         <v>41537</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
@@ -5667,7 +5580,7 @@
         <v>41537</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -5726,7 +5639,7 @@
         <v>41537</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
@@ -5785,7 +5698,7 @@
         <v>41537</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C80" t="s">
         <v>10</v>
@@ -5844,7 +5757,7 @@
         <v>41537</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
@@ -5903,7 +5816,7 @@
         <v>41537</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
         <v>10</v>
@@ -5962,7 +5875,7 @@
         <v>41537</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" t="s">
         <v>10</v>
@@ -6021,7 +5934,7 @@
         <v>41537</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
@@ -6080,7 +5993,7 @@
         <v>41537</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C85" t="s">
         <v>12</v>
@@ -6139,16 +6052,10 @@
         <v>41537</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
-      </c>
-      <c r="D86" t="s">
-        <v>14</v>
-      </c>
-      <c r="E86" t="s">
-        <v>14</v>
       </c>
       <c r="F86">
         <v>731592.9</v>
@@ -6198,7 +6105,7 @@
         <v>41537</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C87" t="s">
         <v>12</v>
@@ -6257,7 +6164,7 @@
         <v>41537</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
@@ -6316,7 +6223,7 @@
         <v>41537</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
@@ -6375,7 +6282,7 @@
         <v>41537</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -6406,24 +6313,6 @@
       </c>
       <c r="L90">
         <v>1.3</v>
-      </c>
-      <c r="M90" t="s">
-        <v>14</v>
-      </c>
-      <c r="N90" t="s">
-        <v>14</v>
-      </c>
-      <c r="O90" t="s">
-        <v>14</v>
-      </c>
-      <c r="P90" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>14</v>
-      </c>
-      <c r="R90" t="s">
-        <v>14</v>
       </c>
       <c r="S90">
         <v>240431</v>
@@ -6434,7 +6323,7 @@
         <v>41537</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
@@ -6493,10 +6382,10 @@
         <v>41537</v>
       </c>
       <c r="B92" t="s">
+        <v>30</v>
+      </c>
+      <c r="C92" t="s">
         <v>31</v>
-      </c>
-      <c r="C92" t="s">
-        <v>32</v>
       </c>
       <c r="D92">
         <v>455.22601320000001</v>
@@ -6552,7 +6441,7 @@
         <v>41537</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -6611,7 +6500,7 @@
         <v>41537</v>
       </c>
       <c r="B94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
@@ -6670,7 +6559,7 @@
         <v>41537</v>
       </c>
       <c r="B95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
@@ -6729,10 +6618,10 @@
         <v>41537</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D96">
         <v>439.66799930000002</v>
@@ -6788,7 +6677,7 @@
         <v>41537</v>
       </c>
       <c r="B97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C97" t="s">
         <v>12</v>
@@ -6847,10 +6736,10 @@
         <v>41537</v>
       </c>
       <c r="B98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D98">
         <v>440.6629944</v>
@@ -6878,24 +6767,6 @@
       </c>
       <c r="L98">
         <v>1.3</v>
-      </c>
-      <c r="M98" t="s">
-        <v>14</v>
-      </c>
-      <c r="N98" t="s">
-        <v>14</v>
-      </c>
-      <c r="O98" t="s">
-        <v>14</v>
-      </c>
-      <c r="P98" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>14</v>
-      </c>
-      <c r="R98" t="s">
-        <v>14</v>
       </c>
       <c r="S98">
         <v>230144</v>
@@ -6906,7 +6777,7 @@
         <v>41537</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
@@ -6965,7 +6836,7 @@
         <v>41537</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
@@ -7024,7 +6895,7 @@
         <v>41537</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
@@ -7083,7 +6954,7 @@
         <v>41537</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
@@ -7142,7 +7013,7 @@
         <v>41537</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C103" t="s">
         <v>12</v>
@@ -7201,10 +7072,10 @@
         <v>41537</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D104">
         <v>445.17898559999998</v>
@@ -7260,7 +7131,7 @@
         <v>41537</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
         <v>12</v>
@@ -7319,7 +7190,7 @@
         <v>41543</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
@@ -7378,10 +7249,10 @@
         <v>41543</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D107">
         <v>115.2089996</v>
@@ -7437,7 +7308,7 @@
         <v>41543</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C108" t="s">
         <v>12</v>
@@ -7496,10 +7367,10 @@
         <v>41543</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D109">
         <v>116.6689987</v>
@@ -7555,10 +7426,10 @@
         <v>41543</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D110">
         <v>117.2740021</v>
@@ -7614,7 +7485,7 @@
         <v>41543</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C111" t="s">
         <v>10</v>
@@ -7673,10 +7544,10 @@
         <v>41543</v>
       </c>
       <c r="B112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D112">
         <v>112.0279999</v>
@@ -7705,23 +7576,8 @@
       <c r="L112">
         <v>1.3</v>
       </c>
-      <c r="M112" t="s">
-        <v>14</v>
-      </c>
-      <c r="N112" t="s">
-        <v>14</v>
-      </c>
-      <c r="O112" t="s">
-        <v>14</v>
-      </c>
       <c r="P112">
         <v>127</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>14</v>
-      </c>
-      <c r="R112" t="s">
-        <v>14</v>
       </c>
       <c r="S112">
         <v>60191</v>
@@ -7732,10 +7588,10 @@
         <v>41543</v>
       </c>
       <c r="B113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D113">
         <v>114.1230011</v>
@@ -7791,10 +7647,10 @@
         <v>41543</v>
       </c>
       <c r="B114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D114">
         <v>110.2330017</v>
@@ -7850,10 +7706,10 @@
         <v>41543</v>
       </c>
       <c r="B115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D115">
         <v>108.81199650000001</v>
@@ -7882,23 +7738,8 @@
       <c r="L115">
         <v>1.3</v>
       </c>
-      <c r="M115" t="s">
-        <v>14</v>
-      </c>
-      <c r="N115" t="s">
-        <v>14</v>
-      </c>
-      <c r="O115" t="s">
-        <v>14</v>
-      </c>
       <c r="P115">
         <v>207</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>14</v>
-      </c>
-      <c r="R115" t="s">
-        <v>14</v>
       </c>
       <c r="S115">
         <v>60039</v>
@@ -7909,10 +7750,10 @@
         <v>41543</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C116" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D116">
         <v>102.8310013</v>
@@ -7968,10 +7809,10 @@
         <v>41543</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D117">
         <v>107.3460007</v>
@@ -8000,23 +7841,8 @@
       <c r="L117">
         <v>1.3</v>
       </c>
-      <c r="M117" t="s">
-        <v>14</v>
-      </c>
-      <c r="N117" t="s">
-        <v>14</v>
-      </c>
-      <c r="O117" t="s">
-        <v>14</v>
-      </c>
       <c r="P117">
         <v>270</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>14</v>
-      </c>
-      <c r="R117" t="s">
-        <v>14</v>
       </c>
       <c r="S117">
         <v>60115</v>
@@ -8027,10 +7853,10 @@
         <v>41543</v>
       </c>
       <c r="B118" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D118">
         <v>104.3330002</v>
@@ -8086,10 +7912,10 @@
         <v>41543</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D119">
         <v>58.870300290000003</v>
@@ -8145,10 +7971,10 @@
         <v>41543</v>
       </c>
       <c r="B120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D120">
         <v>61.728599549999998</v>
@@ -8204,10 +8030,10 @@
         <v>41543</v>
       </c>
       <c r="B121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121">
         <v>59.304901119999997</v>
@@ -8263,10 +8089,10 @@
         <v>41543</v>
       </c>
       <c r="B122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C122" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D122">
         <v>59.756999970000003</v>
@@ -8322,10 +8148,10 @@
         <v>41543</v>
       </c>
       <c r="B123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D123">
         <v>52.649200440000001</v>
@@ -8381,10 +8207,10 @@
         <v>41543</v>
       </c>
       <c r="B124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D124">
         <v>55.898601530000001</v>
@@ -8440,10 +8266,10 @@
         <v>41543</v>
       </c>
       <c r="B125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D125">
         <v>55.097599029999998</v>
@@ -8499,10 +8325,10 @@
         <v>41543</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D126">
         <v>53.419300079999999</v>
@@ -8558,10 +8384,10 @@
         <v>41543</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>66.010696409999994</v>
@@ -8589,12 +8415,6 @@
       </c>
       <c r="L127">
         <v>1.3</v>
-      </c>
-      <c r="M127" t="s">
-        <v>14</v>
-      </c>
-      <c r="N127" t="s">
-        <v>14</v>
       </c>
       <c r="O127">
         <v>4.6100000000000003</v>
@@ -8617,10 +8437,10 @@
         <v>41543</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C128" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D128">
         <v>65.932899480000003</v>
@@ -8676,10 +8496,10 @@
         <v>41543</v>
       </c>
       <c r="B129" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D129">
         <v>66.505203249999994</v>
@@ -8735,10 +8555,10 @@
         <v>41543</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C130" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D130">
         <v>71.728301999999999</v>
@@ -8794,10 +8614,10 @@
         <v>41543</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D131">
         <v>77.469100949999998</v>
@@ -8853,10 +8673,10 @@
         <v>41543</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D132">
         <v>71.61000061</v>
@@ -8912,10 +8732,10 @@
         <v>41543</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D133">
         <v>71.560501099999996</v>
@@ -8971,10 +8791,10 @@
         <v>41543</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D134">
         <v>65.883598329999998</v>
@@ -9030,10 +8850,10 @@
         <v>41543</v>
       </c>
       <c r="B135" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D135">
         <v>64.691802980000006</v>
@@ -9061,12 +8881,6 @@
       </c>
       <c r="L135">
         <v>1.3</v>
-      </c>
-      <c r="M135" t="s">
-        <v>14</v>
-      </c>
-      <c r="N135" t="s">
-        <v>14</v>
       </c>
       <c r="O135">
         <v>3.32</v>
@@ -9089,10 +8903,10 @@
         <v>41543</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D136">
         <v>64.450897220000002</v>
@@ -9148,10 +8962,10 @@
         <v>41543</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D137">
         <v>63.7195015</v>
@@ -9179,12 +8993,6 @@
       </c>
       <c r="L137">
         <v>1.3</v>
-      </c>
-      <c r="M137" t="s">
-        <v>14</v>
-      </c>
-      <c r="N137" t="s">
-        <v>14</v>
       </c>
       <c r="O137">
         <v>4.16</v>
@@ -9207,10 +9015,10 @@
         <v>41543</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D138">
         <v>59.293399809999997</v>
@@ -9266,10 +9074,10 @@
         <v>41543</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D139">
         <v>63.111000060000002</v>
@@ -9325,10 +9133,10 @@
         <v>41543</v>
       </c>
       <c r="B140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D140">
         <v>62.11330032</v>
@@ -9384,10 +9192,10 @@
         <v>41543</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D141">
         <v>63.564998629999998</v>
@@ -9443,10 +9251,10 @@
         <v>41543</v>
       </c>
       <c r="B142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C142" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D142">
         <v>158.99800110000001</v>
@@ -9502,10 +9310,10 @@
         <v>41543</v>
       </c>
       <c r="B143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D143">
         <v>160.36999510000001</v>
@@ -9561,10 +9369,10 @@
         <v>41543</v>
       </c>
       <c r="B144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D144">
         <v>163.09500120000001</v>
@@ -9620,7 +9428,7 @@
         <v>41543</v>
       </c>
       <c r="B145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C145" t="s">
         <v>10</v>
@@ -9679,10 +9487,10 @@
         <v>41543</v>
       </c>
       <c r="B146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C146" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D146">
         <v>159.4349976</v>
@@ -9738,10 +9546,10 @@
         <v>41543</v>
       </c>
       <c r="B147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C147" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D147">
         <v>159.26199339999999</v>
@@ -9797,10 +9605,10 @@
         <v>41543</v>
       </c>
       <c r="B148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C148" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D148">
         <v>156.52099609999999</v>
@@ -9856,10 +9664,10 @@
         <v>41543</v>
       </c>
       <c r="B149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C149" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D149">
         <v>153.18800350000001</v>
@@ -9915,10 +9723,10 @@
         <v>41543</v>
       </c>
       <c r="B150" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C150" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D150">
         <v>146.7120056</v>
@@ -9974,10 +9782,10 @@
         <v>41543</v>
       </c>
       <c r="B151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C151" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D151">
         <v>157.24299619999999</v>
@@ -10033,10 +9841,10 @@
         <v>41543</v>
       </c>
       <c r="B152" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D152">
         <v>155.88900760000001</v>
@@ -10092,10 +9900,10 @@
         <v>41543</v>
       </c>
       <c r="B153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D153">
         <v>162.08900449999999</v>
@@ -10151,10 +9959,10 @@
         <v>41543</v>
       </c>
       <c r="B154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D154">
         <v>162.63699339999999</v>
@@ -10210,10 +10018,10 @@
         <v>41543</v>
       </c>
       <c r="B155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C155" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D155">
         <v>169.32000729999999</v>
@@ -10269,7 +10077,7 @@
         <v>41543</v>
       </c>
       <c r="B156" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C156" t="s">
         <v>10</v>
@@ -10328,10 +10136,10 @@
         <v>41543</v>
       </c>
       <c r="B157" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D157">
         <v>163.29299929999999</v>
@@ -10387,10 +10195,10 @@
         <v>41543</v>
       </c>
       <c r="B158" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C158" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D158">
         <v>160.58299260000001</v>
@@ -10446,10 +10254,10 @@
         <v>41543</v>
       </c>
       <c r="B159" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D159">
         <v>163.08299260000001</v>
@@ -10505,10 +10313,10 @@
         <v>41543</v>
       </c>
       <c r="B160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D160">
         <v>157.0749969</v>
@@ -10536,12 +10344,6 @@
       </c>
       <c r="L160">
         <v>1.3</v>
-      </c>
-      <c r="M160" t="s">
-        <v>14</v>
-      </c>
-      <c r="N160" t="s">
-        <v>14</v>
       </c>
       <c r="O160">
         <v>4.93</v>
@@ -10564,10 +10366,10 @@
         <v>41543</v>
       </c>
       <c r="B161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D161">
         <v>159.2409973</v>
@@ -10623,10 +10425,10 @@
         <v>41543</v>
       </c>
       <c r="B162" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D162">
         <v>152.76100159999999</v>
@@ -10682,10 +10484,10 @@
         <v>41543</v>
       </c>
       <c r="B163" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C163" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D163">
         <v>209.60499569999999</v>
@@ -10741,10 +10543,10 @@
         <v>41543</v>
       </c>
       <c r="B164" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C164" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D164">
         <v>207.9620056</v>
@@ -10800,10 +10602,10 @@
         <v>41543</v>
       </c>
       <c r="B165" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D165">
         <v>206.11300660000001</v>
@@ -10831,12 +10633,6 @@
       </c>
       <c r="L165">
         <v>1.3</v>
-      </c>
-      <c r="M165" t="s">
-        <v>14</v>
-      </c>
-      <c r="N165" t="s">
-        <v>14</v>
       </c>
       <c r="O165">
         <v>2.36</v>
@@ -10859,16 +10655,10 @@
         <v>41543</v>
       </c>
       <c r="B166" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
-      </c>
-      <c r="D166" t="s">
-        <v>14</v>
-      </c>
-      <c r="E166" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F166">
         <v>731592.9</v>
@@ -10918,10 +10708,10 @@
         <v>41543</v>
       </c>
       <c r="B167" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D167">
         <v>206.4530029</v>
@@ -10977,10 +10767,10 @@
         <v>41543</v>
       </c>
       <c r="B168" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C168" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D168">
         <v>207.3399963</v>
@@ -11036,10 +10826,10 @@
         <v>41543</v>
       </c>
       <c r="B169" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C169" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D169">
         <v>205.0379944</v>
@@ -11095,10 +10885,10 @@
         <v>41543</v>
       </c>
       <c r="B170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C170" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D170">
         <v>204.20100400000001</v>
@@ -11154,10 +10944,10 @@
         <v>41543</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C171" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D171">
         <v>203.90199279999999</v>
@@ -11213,10 +11003,10 @@
         <v>41543</v>
       </c>
       <c r="B172" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C172" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D172">
         <v>203.0310059</v>
@@ -11272,10 +11062,10 @@
         <v>41543</v>
       </c>
       <c r="B173" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D173">
         <v>199.6779938</v>
@@ -11331,10 +11121,10 @@
         <v>41543</v>
       </c>
       <c r="B174" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C174" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D174">
         <v>198.9839935</v>
@@ -11390,7 +11180,7 @@
         <v>41543</v>
       </c>
       <c r="B175" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C175" t="s">
         <v>12</v>
@@ -11449,7 +11239,7 @@
         <v>41543</v>
       </c>
       <c r="B176" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C176" t="s">
         <v>12</v>
@@ -11508,10 +11298,10 @@
         <v>41543</v>
       </c>
       <c r="B177" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C177" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D177">
         <v>225.02299500000001</v>
@@ -11567,7 +11357,7 @@
         <v>41543</v>
       </c>
       <c r="B178" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C178" t="s">
         <v>12</v>
@@ -11626,10 +11416,10 @@
         <v>41543</v>
       </c>
       <c r="B179" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C179" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D179">
         <v>225.7749939</v>
@@ -11685,10 +11475,10 @@
         <v>41543</v>
       </c>
       <c r="B180" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C180" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D180">
         <v>227.08799740000001</v>
@@ -11744,10 +11534,10 @@
         <v>41543</v>
       </c>
       <c r="B181" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D181">
         <v>221.77299500000001</v>
@@ -11803,7 +11593,7 @@
         <v>41543</v>
       </c>
       <c r="B182" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C182" t="s">
         <v>12</v>
@@ -11862,10 +11652,10 @@
         <v>41543</v>
       </c>
       <c r="B183" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D183">
         <v>214.7879944</v>
@@ -11921,10 +11711,10 @@
         <v>41543</v>
       </c>
       <c r="B184" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C184" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D184">
         <v>217.30400090000001</v>
@@ -11980,7 +11770,7 @@
         <v>41543</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C185" t="s">
         <v>10</v>
@@ -12039,10 +11829,10 @@
         <v>41543</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C186" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D186">
         <v>236.79400630000001</v>
@@ -12098,10 +11888,10 @@
         <v>41543</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C187" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D187">
         <v>238.6470032</v>
@@ -12157,10 +11947,10 @@
         <v>41543</v>
       </c>
       <c r="B188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D188">
         <v>238.61999510000001</v>
@@ -12216,7 +12006,7 @@
         <v>41543</v>
       </c>
       <c r="B189" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C189" t="s">
         <v>12</v>
@@ -12275,10 +12065,10 @@
         <v>41543</v>
       </c>
       <c r="B190" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C190" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D190">
         <v>240.1089935</v>
@@ -12334,7 +12124,7 @@
         <v>41543</v>
       </c>
       <c r="B191" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C191" t="s">
         <v>10</v>
@@ -12393,7 +12183,7 @@
         <v>41543</v>
       </c>
       <c r="B192" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C192" t="s">
         <v>12</v>
@@ -12452,10 +12242,10 @@
         <v>41543</v>
       </c>
       <c r="B193" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C193" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D193">
         <v>232.80200199999999</v>
@@ -12511,10 +12301,10 @@
         <v>41543</v>
       </c>
       <c r="B194" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C194" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D194">
         <v>228.35400390000001</v>
@@ -12570,7 +12360,7 @@
         <v>41543</v>
       </c>
       <c r="B195" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C195" t="s">
         <v>10</v>
@@ -12629,10 +12419,10 @@
         <v>41543</v>
       </c>
       <c r="B196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C196" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D196">
         <v>236.17300420000001</v>
@@ -12660,12 +12450,6 @@
       </c>
       <c r="L196">
         <v>1.3</v>
-      </c>
-      <c r="M196" t="s">
-        <v>14</v>
-      </c>
-      <c r="N196" t="s">
-        <v>14</v>
       </c>
       <c r="O196">
         <v>2.77</v>
@@ -12688,10 +12472,10 @@
         <v>41543</v>
       </c>
       <c r="B197" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D197">
         <v>236.1529999</v>
@@ -12747,7 +12531,7 @@
         <v>41543</v>
       </c>
       <c r="B198" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C198" t="s">
         <v>12</v>
@@ -12806,7 +12590,7 @@
         <v>41543</v>
       </c>
       <c r="B199" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C199" t="s">
         <v>10</v>
@@ -12865,7 +12649,7 @@
         <v>41543</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C200" t="s">
         <v>12</v>
@@ -12924,7 +12708,7 @@
         <v>41543</v>
       </c>
       <c r="B201" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C201" t="s">
         <v>12</v>
@@ -12983,7 +12767,7 @@
         <v>41543</v>
       </c>
       <c r="B202" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C202" t="s">
         <v>12</v>
@@ -13042,7 +12826,7 @@
         <v>41543</v>
       </c>
       <c r="B203" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C203" t="s">
         <v>12</v>
@@ -13101,7 +12885,7 @@
         <v>41543</v>
       </c>
       <c r="B204" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C204" t="s">
         <v>12</v>
@@ -13160,7 +12944,7 @@
         <v>41543</v>
       </c>
       <c r="B205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C205" t="s">
         <v>12</v>
@@ -13219,7 +13003,7 @@
         <v>41543</v>
       </c>
       <c r="B206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C206" t="s">
         <v>12</v>
@@ -13278,7 +13062,7 @@
         <v>41543</v>
       </c>
       <c r="B207" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C207" t="s">
         <v>12</v>
@@ -13337,10 +13121,10 @@
         <v>41543</v>
       </c>
       <c r="B208" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C208" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D208">
         <v>356.5559998</v>
@@ -13396,7 +13180,7 @@
         <v>41543</v>
       </c>
       <c r="B209" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C209" t="s">
         <v>12</v>
@@ -13455,10 +13239,10 @@
         <v>41543</v>
       </c>
       <c r="B210" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C210" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D210">
         <v>358.64401249999997</v>
@@ -13514,7 +13298,7 @@
         <v>41543</v>
       </c>
       <c r="B211" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C211" t="s">
         <v>12</v>
@@ -13573,7 +13357,7 @@
         <v>41543</v>
       </c>
       <c r="B212" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C212" t="s">
         <v>12</v>
@@ -13632,7 +13416,7 @@
         <v>41543</v>
       </c>
       <c r="B213" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C213" t="s">
         <v>10</v>
@@ -13691,7 +13475,7 @@
         <v>41543</v>
       </c>
       <c r="B214" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C214" t="s">
         <v>10</v>
@@ -13722,12 +13506,6 @@
       </c>
       <c r="L214">
         <v>1.3</v>
-      </c>
-      <c r="M214" t="s">
-        <v>14</v>
-      </c>
-      <c r="N214" t="s">
-        <v>14</v>
       </c>
       <c r="O214">
         <v>2.91</v>
@@ -13750,7 +13528,7 @@
         <v>41543</v>
       </c>
       <c r="B215" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C215" t="s">
         <v>12</v>
@@ -13809,10 +13587,10 @@
         <v>41543</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C216" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D216">
         <v>366.06298829999997</v>
@@ -13868,7 +13646,7 @@
         <v>41543</v>
       </c>
       <c r="B217" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C217" t="s">
         <v>10</v>
@@ -13927,7 +13705,7 @@
         <v>41543</v>
       </c>
       <c r="B218" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C218" t="s">
         <v>12</v>
@@ -13986,7 +13764,7 @@
         <v>41543</v>
       </c>
       <c r="B219" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C219" t="s">
         <v>12</v>
@@ -14045,10 +13823,10 @@
         <v>41543</v>
       </c>
       <c r="B220" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C220" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D220">
         <v>367.81698610000001</v>
@@ -14104,7 +13882,7 @@
         <v>41543</v>
       </c>
       <c r="B221" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C221" t="s">
         <v>12</v>
@@ -14163,7 +13941,7 @@
         <v>41543</v>
       </c>
       <c r="B222" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C222" t="s">
         <v>10</v>
@@ -14194,12 +13972,6 @@
       </c>
       <c r="L222">
         <v>1.3</v>
-      </c>
-      <c r="M222" t="s">
-        <v>14</v>
-      </c>
-      <c r="N222" t="s">
-        <v>14</v>
       </c>
       <c r="O222">
         <v>1.56</v>
@@ -14222,10 +13994,10 @@
         <v>41543</v>
       </c>
       <c r="B223" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C223" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D223">
         <v>362.61199950000002</v>
@@ -14253,12 +14025,6 @@
       </c>
       <c r="L223">
         <v>1.3</v>
-      </c>
-      <c r="M223" t="s">
-        <v>14</v>
-      </c>
-      <c r="N223" t="s">
-        <v>14</v>
       </c>
       <c r="O223">
         <v>3.65</v>
@@ -14281,7 +14047,7 @@
         <v>41543</v>
       </c>
       <c r="B224" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C224" t="s">
         <v>11</v>
@@ -14340,10 +14106,10 @@
         <v>41543</v>
       </c>
       <c r="B225" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C225" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D225">
         <v>258.5899963</v>
@@ -14371,12 +14137,6 @@
       </c>
       <c r="L225">
         <v>1.3</v>
-      </c>
-      <c r="M225" t="s">
-        <v>14</v>
-      </c>
-      <c r="N225" t="s">
-        <v>14</v>
       </c>
       <c r="O225">
         <v>2.86</v>
@@ -14399,10 +14159,10 @@
         <v>41543</v>
       </c>
       <c r="B226" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C226" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D226">
         <v>260.63900760000001</v>
@@ -14458,10 +14218,10 @@
         <v>41543</v>
       </c>
       <c r="B227" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C227" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D227">
         <v>263.18301389999999</v>
@@ -14517,10 +14277,10 @@
         <v>41543</v>
       </c>
       <c r="B228" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C228" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D228">
         <v>264.71798710000002</v>
@@ -14576,7 +14336,7 @@
         <v>41543</v>
       </c>
       <c r="B229" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C229" t="s">
         <v>10</v>
@@ -14635,7 +14395,7 @@
         <v>41543</v>
       </c>
       <c r="B230" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C230" t="s">
         <v>10</v>
@@ -14694,10 +14454,10 @@
         <v>41543</v>
       </c>
       <c r="B231" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C231" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D231">
         <v>259.4129944</v>
@@ -14725,12 +14485,6 @@
       </c>
       <c r="L231">
         <v>1.3</v>
-      </c>
-      <c r="M231" t="s">
-        <v>14</v>
-      </c>
-      <c r="N231" t="s">
-        <v>14</v>
       </c>
       <c r="O231">
         <v>4.46</v>
@@ -14753,10 +14507,10 @@
         <v>41543</v>
       </c>
       <c r="B232" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C232" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D232">
         <v>252.71800229999999</v>
@@ -14812,10 +14566,10 @@
         <v>41543</v>
       </c>
       <c r="B233" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C233" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D233">
         <v>256.59799190000001</v>
@@ -14871,10 +14625,10 @@
         <v>41543</v>
       </c>
       <c r="B234" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C234" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D234">
         <v>253.81399540000001</v>
@@ -14930,10 +14684,10 @@
         <v>41543</v>
       </c>
       <c r="B235" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C235" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D235">
         <v>257.30700680000001</v>
@@ -14989,7 +14743,7 @@
         <v>41543</v>
       </c>
       <c r="B236" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C236" t="s">
         <v>10</v>
@@ -15048,10 +14802,10 @@
         <v>41550</v>
       </c>
       <c r="B237" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C237" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D237">
         <v>262.9970093</v>
@@ -15107,10 +14861,10 @@
         <v>41550</v>
       </c>
       <c r="B238" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C238" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D238">
         <v>261.97698969999999</v>
@@ -15166,10 +14920,10 @@
         <v>41550</v>
       </c>
       <c r="B239" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C239" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D239">
         <v>258.77899170000001</v>
@@ -15225,7 +14979,7 @@
         <v>41550</v>
       </c>
       <c r="B240" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C240" t="s">
         <v>10</v>
@@ -15284,10 +15038,10 @@
         <v>41550</v>
       </c>
       <c r="B241" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D241">
         <v>259.60800169999999</v>
@@ -15316,17 +15070,8 @@
       <c r="L241">
         <v>1.3</v>
       </c>
-      <c r="M241" t="s">
-        <v>14</v>
-      </c>
-      <c r="N241" t="s">
-        <v>14</v>
-      </c>
       <c r="O241">
         <v>2.4300000000000002</v>
-      </c>
-      <c r="P241" t="s">
-        <v>14</v>
       </c>
       <c r="Q241" s="2">
         <v>2.9800000000000001E-16</v>
@@ -15343,10 +15088,10 @@
         <v>41550</v>
       </c>
       <c r="B242" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C242" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D242">
         <v>250.88600159999999</v>
@@ -15402,7 +15147,7 @@
         <v>41550</v>
       </c>
       <c r="B243" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C243" t="s">
         <v>10</v>
@@ -15461,10 +15206,10 @@
         <v>41550</v>
       </c>
       <c r="B244" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C244" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D244">
         <v>266.118988</v>
@@ -15520,7 +15265,7 @@
         <v>41550</v>
       </c>
       <c r="B245" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C245" t="s">
         <v>12</v>
@@ -15545,12 +15290,6 @@
       </c>
       <c r="J245">
         <v>39.4</v>
-      </c>
-      <c r="K245" t="s">
-        <v>14</v>
-      </c>
-      <c r="L245" t="s">
-        <v>14</v>
       </c>
       <c r="M245">
         <v>1.81</v>
@@ -15579,7 +15318,7 @@
         <v>41550</v>
       </c>
       <c r="B246" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C246" t="s">
         <v>12</v>
@@ -15638,10 +15377,10 @@
         <v>41550</v>
       </c>
       <c r="B247" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D247">
         <v>331.13500979999998</v>
@@ -15697,10 +15436,10 @@
         <v>41550</v>
       </c>
       <c r="B248" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C248" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D248">
         <v>328.23999020000002</v>
@@ -15756,7 +15495,7 @@
         <v>41550</v>
       </c>
       <c r="B249" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C249" t="s">
         <v>10</v>
@@ -15815,7 +15554,7 @@
         <v>41550</v>
       </c>
       <c r="B250" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C250" t="s">
         <v>12</v>
@@ -15874,10 +15613,10 @@
         <v>41550</v>
       </c>
       <c r="B251" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C251" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D251">
         <v>329.3340149</v>
@@ -15933,10 +15672,10 @@
         <v>41550</v>
       </c>
       <c r="B252" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C252" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D252">
         <v>333.14099119999997</v>
@@ -15992,7 +15731,7 @@
         <v>41550</v>
       </c>
       <c r="B253" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C253" t="s">
         <v>12</v>
@@ -16051,7 +15790,7 @@
         <v>41550</v>
       </c>
       <c r="B254" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C254" t="s">
         <v>12</v>
@@ -16110,7 +15849,7 @@
         <v>41550</v>
       </c>
       <c r="B255" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C255" t="s">
         <v>12</v>
@@ -16169,10 +15908,10 @@
         <v>41550</v>
       </c>
       <c r="B256" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C256" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D256">
         <v>257.5840149</v>
@@ -16228,7 +15967,7 @@
         <v>41550</v>
       </c>
       <c r="B257" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C257" t="s">
         <v>12</v>
@@ -16287,7 +16026,7 @@
         <v>41550</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C258" t="s">
         <v>12</v>
@@ -16346,10 +16085,10 @@
         <v>41550</v>
       </c>
       <c r="B259" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C259" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D259">
         <v>260.87701420000002</v>
@@ -16405,7 +16144,7 @@
         <v>41550</v>
       </c>
       <c r="B260" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C260" t="s">
         <v>12</v>
@@ -16464,10 +16203,10 @@
         <v>41550</v>
       </c>
       <c r="B261" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C261" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D261">
         <v>252.6840057</v>
@@ -16523,10 +16262,10 @@
         <v>41550</v>
       </c>
       <c r="B262" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C262" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D262">
         <v>250.35499569999999</v>
@@ -16582,7 +16321,7 @@
         <v>41550</v>
       </c>
       <c r="B263" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C263" t="s">
         <v>12</v>
@@ -16641,10 +16380,10 @@
         <v>41550</v>
       </c>
       <c r="B264" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C264" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D264">
         <v>255.871994</v>
@@ -16700,10 +16439,10 @@
         <v>41550</v>
       </c>
       <c r="B265" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C265" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D265">
         <v>181.8370056</v>
@@ -16759,10 +16498,10 @@
         <v>41550</v>
       </c>
       <c r="B266" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C266" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D266">
         <v>179.07400509999999</v>
@@ -16818,10 +16557,10 @@
         <v>41550</v>
       </c>
       <c r="B267" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C267" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D267">
         <v>179.04299929999999</v>
@@ -16877,10 +16616,10 @@
         <v>41550</v>
       </c>
       <c r="B268" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C268" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D268">
         <v>175.98199460000001</v>
@@ -16936,10 +16675,10 @@
         <v>41550</v>
       </c>
       <c r="B269" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C269" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D269">
         <v>181.96600340000001</v>
@@ -16995,10 +16734,10 @@
         <v>41550</v>
       </c>
       <c r="B270" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C270" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D270">
         <v>181.4499969</v>
@@ -17054,10 +16793,10 @@
         <v>41550</v>
       </c>
       <c r="B271" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C271" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D271">
         <v>185.23599239999999</v>
@@ -17113,10 +16852,10 @@
         <v>41550</v>
       </c>
       <c r="B272" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C272" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D272">
         <v>192.0350037</v>
@@ -17172,10 +16911,10 @@
         <v>41550</v>
       </c>
       <c r="B273" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C273" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D273">
         <v>195.0350037</v>
@@ -17231,10 +16970,10 @@
         <v>41550</v>
       </c>
       <c r="B274" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C274" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D274">
         <v>196.8220062</v>
@@ -17290,7 +17029,7 @@
         <v>41550</v>
       </c>
       <c r="B275" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C275" t="s">
         <v>10</v>
@@ -17349,10 +17088,10 @@
         <v>41550</v>
       </c>
       <c r="B276" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C276" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D276">
         <v>200.07299800000001</v>
@@ -17408,10 +17147,10 @@
         <v>41550</v>
       </c>
       <c r="B277" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C277" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D277">
         <v>191.64300539999999</v>
@@ -17467,7 +17206,7 @@
         <v>41550</v>
       </c>
       <c r="B278" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C278" t="s">
         <v>10</v>
@@ -17526,10 +17265,10 @@
         <v>41550</v>
       </c>
       <c r="B279" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C279" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D279">
         <v>188.2339935</v>
@@ -17585,10 +17324,10 @@
         <v>41550</v>
       </c>
       <c r="B280" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C280" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D280">
         <v>187.1779938</v>
@@ -17644,7 +17383,7 @@
         <v>41550</v>
       </c>
       <c r="B281" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C281" t="s">
         <v>10</v>
@@ -17703,7 +17442,7 @@
         <v>41550</v>
       </c>
       <c r="B282" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C282" t="s">
         <v>10</v>
@@ -17762,10 +17501,10 @@
         <v>41550</v>
       </c>
       <c r="B283" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C283" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D283">
         <v>123.9940033</v>
@@ -17821,7 +17560,7 @@
         <v>41550</v>
       </c>
       <c r="B284" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C284" t="s">
         <v>12</v>
@@ -17880,10 +17619,10 @@
         <v>41550</v>
       </c>
       <c r="B285" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C285" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D285">
         <v>123.487999</v>
@@ -17908,15 +17647,6 @@
       </c>
       <c r="K285">
         <v>15.2</v>
-      </c>
-      <c r="L285" t="s">
-        <v>14</v>
-      </c>
-      <c r="M285" t="s">
-        <v>14</v>
-      </c>
-      <c r="N285" t="s">
-        <v>14</v>
       </c>
       <c r="O285">
         <v>2.23</v>
@@ -17939,10 +17669,10 @@
         <v>41550</v>
       </c>
       <c r="B286" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C286" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D286">
         <v>120.9420013</v>
@@ -17998,10 +17728,10 @@
         <v>41550</v>
       </c>
       <c r="B287" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C287" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D287">
         <v>116.7679977</v>
@@ -18057,10 +17787,10 @@
         <v>41550</v>
       </c>
       <c r="B288" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C288" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D288">
         <v>119.83799740000001</v>
@@ -18116,10 +17846,10 @@
         <v>41550</v>
       </c>
       <c r="B289" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C289" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D289">
         <v>118.1729965</v>
@@ -18175,10 +17905,10 @@
         <v>41550</v>
       </c>
       <c r="B290" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C290" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D290">
         <v>119.8580017</v>
@@ -18203,15 +17933,6 @@
       </c>
       <c r="K290">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="L290" t="s">
-        <v>14</v>
-      </c>
-      <c r="M290" t="s">
-        <v>14</v>
-      </c>
-      <c r="N290" t="s">
-        <v>14</v>
       </c>
       <c r="O290">
         <v>2.21</v>
@@ -18234,10 +17955,10 @@
         <v>41550</v>
       </c>
       <c r="B291" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C291" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D291">
         <v>114.3219986</v>
@@ -18293,7 +18014,7 @@
         <v>41550</v>
       </c>
       <c r="B292" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C292" t="s">
         <v>10</v>
@@ -18352,10 +18073,10 @@
         <v>41550</v>
       </c>
       <c r="B293" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C293" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D293">
         <v>121.29299930000001</v>
@@ -18411,10 +18132,10 @@
         <v>41550</v>
       </c>
       <c r="B294" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C294" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D294">
         <v>121.4250031</v>
@@ -18439,15 +18160,6 @@
       </c>
       <c r="K294">
         <v>2.7</v>
-      </c>
-      <c r="L294" t="s">
-        <v>14</v>
-      </c>
-      <c r="M294" t="s">
-        <v>14</v>
-      </c>
-      <c r="N294" t="s">
-        <v>14</v>
       </c>
       <c r="O294">
         <v>1.8</v>
@@ -18470,10 +18182,10 @@
         <v>41550</v>
       </c>
       <c r="B295" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C295" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D295">
         <v>124.5289993</v>
@@ -18529,10 +18241,10 @@
         <v>41550</v>
       </c>
       <c r="B296" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C296" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D296">
         <v>124.512001</v>
@@ -18588,10 +18300,10 @@
         <v>41550</v>
       </c>
       <c r="B297" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C297" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D297">
         <v>96.640403750000004</v>
@@ -18647,10 +18359,10 @@
         <v>41550</v>
       </c>
       <c r="B298" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C298" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D298">
         <v>100.36799619999999</v>
@@ -18706,10 +18418,10 @@
         <v>41550</v>
       </c>
       <c r="B299" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C299" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D299">
         <v>101.052002</v>
@@ -18765,10 +18477,10 @@
         <v>41550</v>
       </c>
       <c r="B300" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C300" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D300">
         <v>101.8079987</v>
@@ -18824,10 +18536,10 @@
         <v>41550</v>
       </c>
       <c r="B301" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C301" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D301">
         <v>106.8059998</v>
@@ -18883,7 +18595,7 @@
         <v>41550</v>
       </c>
       <c r="B302" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C302" t="s">
         <v>12</v>
@@ -18942,10 +18654,10 @@
         <v>41550</v>
       </c>
       <c r="B303" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C303" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D303">
         <v>99.310897830000002</v>
@@ -19001,10 +18713,10 @@
         <v>41550</v>
       </c>
       <c r="B304" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C304" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D304">
         <v>96.358802800000007</v>
@@ -19060,7 +18772,7 @@
         <v>41550</v>
       </c>
       <c r="B305" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C305" t="s">
         <v>10</v>
@@ -19119,10 +18831,10 @@
         <v>41550</v>
       </c>
       <c r="B306" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C306" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D306">
         <v>93.182403559999997</v>
@@ -19178,16 +18890,10 @@
         <v>41550</v>
       </c>
       <c r="B307" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C307" t="s">
         <v>11</v>
-      </c>
-      <c r="D307" t="s">
-        <v>14</v>
-      </c>
-      <c r="E307" t="s">
-        <v>14</v>
       </c>
       <c r="F307">
         <v>731592.9</v>
@@ -19237,10 +18943,10 @@
         <v>41550</v>
       </c>
       <c r="B308" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C308" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D308">
         <v>17.44029999</v>
@@ -19296,7 +19002,7 @@
         <v>41550</v>
       </c>
       <c r="B309" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C309" t="s">
         <v>12</v>
@@ -19355,10 +19061,10 @@
         <v>41550</v>
       </c>
       <c r="B310" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C310" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D310">
         <v>17.11009979</v>
@@ -19414,10 +19120,10 @@
         <v>41550</v>
       </c>
       <c r="B311" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C311" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D311">
         <v>17.016199109999999</v>
@@ -19473,10 +19179,10 @@
         <v>41550</v>
       </c>
       <c r="B312" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C312" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D312">
         <v>16.135700230000001</v>
@@ -19532,7 +19238,7 @@
         <v>41550</v>
       </c>
       <c r="B313" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C313" t="s">
         <v>12</v>
@@ -19591,10 +19297,10 @@
         <v>41550</v>
       </c>
       <c r="B314" t="s">
+        <v>53</v>
+      </c>
+      <c r="C314" t="s">
         <v>54</v>
-      </c>
-      <c r="C314" t="s">
-        <v>55</v>
       </c>
       <c r="D314">
         <v>14.22469997</v>
@@ -19650,7 +19356,7 @@
         <v>41550</v>
       </c>
       <c r="B315" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C315" t="s">
         <v>10</v>
@@ -19709,7 +19415,7 @@
         <v>41550</v>
       </c>
       <c r="B316" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C316" t="s">
         <v>10</v>
@@ -19768,10 +19474,10 @@
         <v>41550</v>
       </c>
       <c r="B317" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C317" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D317">
         <v>27.515100480000001</v>
@@ -19827,10 +19533,10 @@
         <v>41550</v>
       </c>
       <c r="B318" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C318" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D318">
         <v>21.43110085</v>
@@ -19886,10 +19592,10 @@
         <v>41550</v>
       </c>
       <c r="B319" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C319" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D319">
         <v>19.41040039</v>
@@ -19945,10 +19651,10 @@
         <v>41550</v>
       </c>
       <c r="B320" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C320" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D320">
         <v>23.387100220000001</v>
@@ -20004,7 +19710,7 @@
         <v>41550</v>
       </c>
       <c r="B321" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C321" t="s">
         <v>12</v>
@@ -20063,10 +19769,10 @@
         <v>41550</v>
       </c>
       <c r="B322" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C322" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D322">
         <v>22.80529976</v>
@@ -20122,10 +19828,10 @@
         <v>41550</v>
       </c>
       <c r="B323" t="s">
+        <v>55</v>
+      </c>
+      <c r="C323" t="s">
         <v>56</v>
-      </c>
-      <c r="C323" t="s">
-        <v>57</v>
       </c>
       <c r="D323">
         <v>28.15010071</v>
@@ -20181,10 +19887,10 @@
         <v>41550</v>
       </c>
       <c r="B324" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C324" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D324">
         <v>29.428800580000001</v>
@@ -20240,10 +19946,10 @@
         <v>41550</v>
       </c>
       <c r="B325" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C325" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D325">
         <v>35.06510162</v>
@@ -20299,10 +20005,10 @@
         <v>41550</v>
       </c>
       <c r="B326" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C326" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D326">
         <v>36.277400970000002</v>
@@ -20327,15 +20033,6 @@
       </c>
       <c r="K326">
         <v>10.7</v>
-      </c>
-      <c r="L326" t="s">
-        <v>14</v>
-      </c>
-      <c r="M326" t="s">
-        <v>14</v>
-      </c>
-      <c r="N326" t="s">
-        <v>14</v>
       </c>
       <c r="O326">
         <v>8.26</v>
@@ -20358,10 +20055,10 @@
         <v>41550</v>
       </c>
       <c r="B327" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C327" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D327">
         <v>28.615100859999998</v>
@@ -20417,10 +20114,10 @@
         <v>41550</v>
       </c>
       <c r="B328" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C328" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D328">
         <v>30.360200880000001</v>
@@ -20476,10 +20173,10 @@
         <v>41551</v>
       </c>
       <c r="B329" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C329" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D329">
         <v>676.00897220000002</v>
@@ -20535,10 +20232,10 @@
         <v>41551</v>
       </c>
       <c r="B330" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C330" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D330">
         <v>679.32702640000002</v>
@@ -20594,10 +20291,10 @@
         <v>41551</v>
       </c>
       <c r="B331" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C331" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D331">
         <v>670.23602289999997</v>
@@ -20653,10 +20350,10 @@
         <v>41551</v>
       </c>
       <c r="B332" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C332" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D332">
         <v>671.85400389999995</v>
@@ -20712,10 +20409,10 @@
         <v>41551</v>
       </c>
       <c r="B333" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C333" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D333">
         <v>669.01599120000003</v>
@@ -20771,10 +20468,10 @@
         <v>41551</v>
       </c>
       <c r="B334" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C334" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D334">
         <v>671.64599610000005</v>
@@ -20799,15 +20496,6 @@
       </c>
       <c r="K334">
         <v>1.6</v>
-      </c>
-      <c r="L334" t="s">
-        <v>14</v>
-      </c>
-      <c r="M334" t="s">
-        <v>14</v>
-      </c>
-      <c r="N334" t="s">
-        <v>14</v>
       </c>
       <c r="O334">
         <v>1.82</v>
@@ -20830,7 +20518,7 @@
         <v>41551</v>
       </c>
       <c r="B335" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C335" t="s">
         <v>10</v>
@@ -20889,7 +20577,7 @@
         <v>41551</v>
       </c>
       <c r="B336" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C336" t="s">
         <v>10</v>
@@ -20948,10 +20636,10 @@
         <v>41551</v>
       </c>
       <c r="B337" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C337" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D337">
         <v>671.73999019999997</v>
@@ -21007,7 +20695,7 @@
         <v>41551</v>
       </c>
       <c r="B338" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C338" t="s">
         <v>11</v>
@@ -21066,7 +20754,7 @@
         <v>41551</v>
       </c>
       <c r="B339" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C339" t="s">
         <v>11</v>
@@ -21094,15 +20782,6 @@
       </c>
       <c r="K339">
         <v>3</v>
-      </c>
-      <c r="L339" t="s">
-        <v>14</v>
-      </c>
-      <c r="M339" t="s">
-        <v>14</v>
-      </c>
-      <c r="N339" t="s">
-        <v>14</v>
       </c>
       <c r="O339">
         <v>4.08</v>
@@ -21125,10 +20804,10 @@
         <v>41551</v>
       </c>
       <c r="B340" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C340" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D340">
         <v>676.03802489999998</v>
@@ -21184,10 +20863,10 @@
         <v>41551</v>
       </c>
       <c r="B341" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C341" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D341">
         <v>676.00897220000002</v>
@@ -21243,10 +20922,10 @@
         <v>41551</v>
       </c>
       <c r="B342" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C342" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D342">
         <v>681.66198729999996</v>
@@ -21302,10 +20981,10 @@
         <v>41551</v>
       </c>
       <c r="B343" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C343" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D343">
         <v>637.72198490000005</v>
@@ -21330,15 +21009,6 @@
       </c>
       <c r="K343">
         <v>5.8</v>
-      </c>
-      <c r="L343" t="s">
-        <v>14</v>
-      </c>
-      <c r="M343" t="s">
-        <v>14</v>
-      </c>
-      <c r="N343" t="s">
-        <v>14</v>
       </c>
       <c r="O343">
         <v>2.1800000000000002</v>
@@ -21361,7 +21031,7 @@
         <v>41551</v>
       </c>
       <c r="B344" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C344" t="s">
         <v>11</v>
@@ -21420,7 +21090,7 @@
         <v>41551</v>
       </c>
       <c r="B345" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C345" t="s">
         <v>10</v>
@@ -21479,7 +21149,7 @@
         <v>41551</v>
       </c>
       <c r="B346" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C346" t="s">
         <v>10</v>
@@ -21507,15 +21177,6 @@
       </c>
       <c r="K346">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="L346" t="s">
-        <v>14</v>
-      </c>
-      <c r="M346" t="s">
-        <v>14</v>
-      </c>
-      <c r="N346" t="s">
-        <v>14</v>
       </c>
       <c r="O346">
         <v>4.9000000000000004</v>
@@ -21538,7 +21199,7 @@
         <v>41551</v>
       </c>
       <c r="B347" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C347" t="s">
         <v>12</v>
@@ -21597,10 +21258,10 @@
         <v>41551</v>
       </c>
       <c r="B348" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C348" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D348">
         <v>635.2069702</v>
@@ -21656,10 +21317,10 @@
         <v>41551</v>
       </c>
       <c r="B349" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C349" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D349">
         <v>661.33300780000002</v>
@@ -21715,10 +21376,10 @@
         <v>41551</v>
       </c>
       <c r="B350" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C350" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D350">
         <v>661.95501709999996</v>
@@ -21774,10 +21435,10 @@
         <v>41551</v>
       </c>
       <c r="B351" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C351" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D351">
         <v>663.04400629999998</v>
@@ -21833,10 +21494,10 @@
         <v>41551</v>
       </c>
       <c r="B352" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C352" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D352">
         <v>663.71398929999998</v>
@@ -21892,7 +21553,7 @@
         <v>41551</v>
       </c>
       <c r="B353" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C353" t="s">
         <v>10</v>
@@ -21951,10 +21612,10 @@
         <v>41551</v>
       </c>
       <c r="B354" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C354" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D354">
         <v>668.01098630000001</v>
@@ -22010,10 +21671,10 @@
         <v>41551</v>
       </c>
       <c r="B355" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C355" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D355">
         <v>663.28802489999998</v>
@@ -22069,10 +21730,10 @@
         <v>41551</v>
       </c>
       <c r="B356" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C356" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D356">
         <v>662.375</v>
@@ -22097,15 +21758,6 @@
       </c>
       <c r="K356">
         <v>2.7</v>
-      </c>
-      <c r="L356" t="s">
-        <v>14</v>
-      </c>
-      <c r="M356" t="s">
-        <v>14</v>
-      </c>
-      <c r="N356" t="s">
-        <v>14</v>
       </c>
       <c r="O356">
         <v>3.02</v>
@@ -22128,10 +21780,10 @@
         <v>41551</v>
       </c>
       <c r="B357" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C357" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D357">
         <v>661.43798830000003</v>
@@ -22187,7 +21839,7 @@
         <v>41551</v>
       </c>
       <c r="B358" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C358" t="s">
         <v>12</v>
@@ -22246,7 +21898,7 @@
         <v>41551</v>
       </c>
       <c r="B359" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C359" t="s">
         <v>12</v>
@@ -22305,10 +21957,10 @@
         <v>41551</v>
       </c>
       <c r="B360" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C360" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D360">
         <v>660.08300780000002</v>
@@ -22364,7 +22016,7 @@
         <v>41551</v>
       </c>
       <c r="B361" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C361" t="s">
         <v>11</v>
@@ -22423,7 +22075,7 @@
         <v>41551</v>
       </c>
       <c r="B362" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C362" t="s">
         <v>11</v>
@@ -22482,10 +22134,10 @@
         <v>41551</v>
       </c>
       <c r="B363" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C363" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D363">
         <v>675.23498540000003</v>
@@ -22541,10 +22193,10 @@
         <v>41551</v>
       </c>
       <c r="B364" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C364" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D364">
         <v>675.70898439999996</v>
@@ -22600,10 +22252,10 @@
         <v>41551</v>
       </c>
       <c r="B365" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C365" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D365">
         <v>678.02197269999999</v>
@@ -22659,10 +22311,10 @@
         <v>41551</v>
       </c>
       <c r="B366" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C366" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D366">
         <v>676.05297849999999</v>
@@ -22718,10 +22370,10 @@
         <v>41551</v>
       </c>
       <c r="B367" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C367" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D367">
         <v>674.43298340000001</v>
@@ -22777,7 +22429,7 @@
         <v>41551</v>
       </c>
       <c r="B368" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C368" t="s">
         <v>12</v>
@@ -22836,10 +22488,10 @@
         <v>41551</v>
       </c>
       <c r="B369" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C369" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D369">
         <v>677.83398439999996</v>
@@ -22895,7 +22547,7 @@
         <v>41551</v>
       </c>
       <c r="B370" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C370" t="s">
         <v>10</v>
@@ -22954,16 +22606,10 @@
         <v>41551</v>
       </c>
       <c r="B371" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C371" t="s">
         <v>10</v>
-      </c>
-      <c r="D371" t="s">
-        <v>14</v>
-      </c>
-      <c r="E371" t="s">
-        <v>14</v>
       </c>
       <c r="F371">
         <v>731592.9</v>
@@ -23013,7 +22659,7 @@
         <v>41551</v>
       </c>
       <c r="B372" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C372" t="s">
         <v>12</v>
@@ -23072,7 +22718,7 @@
         <v>41551</v>
       </c>
       <c r="B373" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C373" t="s">
         <v>10</v>
@@ -23100,15 +22746,6 @@
       </c>
       <c r="K373">
         <v>5</v>
-      </c>
-      <c r="L373" t="s">
-        <v>14</v>
-      </c>
-      <c r="M373" t="s">
-        <v>14</v>
-      </c>
-      <c r="N373" t="s">
-        <v>14</v>
       </c>
       <c r="O373">
         <v>4.1399999999999997</v>
@@ -23131,7 +22768,7 @@
         <v>41551</v>
       </c>
       <c r="B374" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C374" t="s">
         <v>10</v>
@@ -23190,10 +22827,10 @@
         <v>41551</v>
       </c>
       <c r="B375" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C375" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D375">
         <v>548.57897949999995</v>
